--- a/tasks/finalpool/notion-fetch-competitor/groundtruth_workspace/Competitor_Analysis.xlsx
+++ b/tasks/finalpool/notion-fetch-competitor/groundtruth_workspace/Competitor_Analysis.xlsx
@@ -7,8 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product Listing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detailed Analysis" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product Comparison" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SWOT Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,209 +415,176 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Price</t>
+          <t>Product_Name</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>Pricing_Tier</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Monthly_Price</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Key_Features</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Target_Market</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>Rating</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Features</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Gamma Ultra</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>499</v>
-      </c>
-      <c r="C2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Premium, AI-Powered</t>
-        </is>
+          <t>ProjectHub Inc</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ProjectHub 360</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>pro</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Task Management, Kanban Boards, Built-in Chat, Video Conferencing, Time Tracking, Custom Fields</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Small to mid-size teams needing collaboration tools</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>4.3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Zeta Max</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>599</v>
-      </c>
-      <c r="C3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>High-Performance, Enterprise</t>
-        </is>
+          <t>AgileBoard Co</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AgileBoard Pro</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>15</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Kanban Boards, Scrum Support, Sprint Planning, Backlog Management, Burndown Charts, API Access</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Agile development teams and software companies</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>4.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Iota Edge</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>399</v>
-      </c>
-      <c r="C4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Cutting-Edge, Innovative</t>
-        </is>
+          <t>WorkStream Ltd</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>WorkStream Suite</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>growth</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>20</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Task Management, Document Management, Workflow Automation, Time Tracking, Resource Allocation, Client Portal, Invoicing</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Professional services firms and agencies</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>4.1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alpha Pro</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>299</v>
-      </c>
-      <c r="C5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Fast, Reliable</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Epsilon Core</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>349</v>
-      </c>
-      <c r="C6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Scalable, Secure</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Beta Suite</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>199</v>
-      </c>
-      <c r="C7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Affordable, User-Friendly</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Theta Plus</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>249</v>
-      </c>
-      <c r="C8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Versatile, Modular</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Kappa Flex</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>159</v>
-      </c>
-      <c r="C9" t="n">
-        <v>4</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Flexible, Customizable</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Delta Lite</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>89</v>
-      </c>
-      <c r="C10" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Lightweight, Portable</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Eta Basic</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>49</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Budget, Simple</t>
-        </is>
+          <t>TeamSync Corp</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TeamSync Platform</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>business</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>28</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Task Management, Gantt Charts, AI Task Suggestions, Resource Allocation, Reporting Dashboard, Custom Workflows, Goal Tracking</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Enterprise teams and large organizations</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>4.4</v>
       </c>
     </row>
   </sheetData>
@@ -630,142 +598,461 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Feature_Name</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Price</t>
+          <t>Our_Product</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rating</t>
+          <t>Competitor_A</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Competitor_B</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Pros</t>
+          <t>Competitor_C</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Cons</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Target_Market</t>
+          <t>Competitor_D</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alpha Pro</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>299</v>
-      </c>
-      <c r="C2" t="n">
-        <v>4.5</v>
+          <t>Task Management</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>The Alpha Pro is a mid-range solution designed for small to medium businesses that need reliable performance without breaking the bank. It combines speed with dependability, offering consistent uptime and fast processing for everyday workloads.</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Excellent reliability with 99.9% uptime guarantee; Fast boot and processing times; Strong customer support with 24/7 availability</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Limited advanced analytics features; No built-in AI capabilities</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Small to medium businesses seeking dependable performance at a reasonable price point.</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Gamma Ultra</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>499</v>
-      </c>
-      <c r="C3" t="n">
-        <v>4.8</v>
+          <t>Kanban Boards</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>The Gamma Ultra is the flagship premium product featuring cutting-edge AI-powered automation and analytics. It offers unmatched performance for data-intensive operations and is designed for organizations that demand the best technology available.</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>State-of-the-art AI and machine learning integration; Superior performance benchmarks across all categories; Comprehensive analytics dashboard</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>High price point may be prohibitive for smaller teams; Steeper learning curve for new users</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Large enterprises and data-driven organizations requiring premium AI-powered capabilities.</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Zeta Max</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>599</v>
-      </c>
-      <c r="C4" t="n">
-        <v>4.7</v>
+          <t>Time Tracking</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>The Zeta Max is the ultimate enterprise solution built for high-performance computing environments. It delivers exceptional throughput and is designed to handle the most demanding workloads at scale with enterprise-grade security and compliance features.</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Unparalleled performance for enterprise workloads; Advanced security and compliance certifications; Dedicated enterprise support team</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Most expensive option in the lineup; Requires dedicated infrastructure for optimal performance</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Enterprise organizations with high-performance computing needs and strict security requirements.</t>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gantt Charts</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Resource Allocation</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Custom Workflows</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>API Access</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Reporting Dashboard</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Strength</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Intuitive UI and competitive pricing relative to enterprise competitors</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Strength</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Strong integrations ecosystem appeals to mid-size teams</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Weakness</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Limited AI features compared to TeamSync's AI Task Suggestions</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Weakness</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>No built-in chat unlike ProjectHub 360</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Add AI capabilities to compete with TeamSync's enterprise positioning</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Expand to professional services market currently dominated by WorkStream</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Threat</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>TeamSync's AI features may attract enterprise customers</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Threat</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ProjectHub's all-in-one collaboration platform may capture mid-market</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>
